--- a/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
   <si>
-    <t>技能Tag</t>
+    <t>技能动画标签</t>
   </si>
   <si>
     <t>技能CD</t>
@@ -41,7 +41,7 @@
     <t>#Note</t>
   </si>
   <si>
-    <t>PlayerSkillTag</t>
+    <t>SkillAniTag</t>
   </si>
   <si>
     <t>CD</t>
@@ -53,16 +53,13 @@
     <t>string</t>
   </si>
   <si>
-    <t>PlayerSkillTagEnum</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>普通攻击</t>
   </si>
   <si>
-    <t>NormalAttack</t>
+    <t>skill_1</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1000,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="20.125" customWidth="1"/>
-    <col min="5" max="5" width="28.375" customWidth="1"/>
+    <col min="5" max="5" width="18.25" customWidth="1"/>
     <col min="6" max="6" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1011,7 +1008,6 @@
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1041,10 +1037,10 @@
         <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1054,10 +1050,10 @@
         <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
       <c r="F6" s="2">
         <v>2000</v>

--- a/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -1001,7 +1001,8 @@
   <cols>
     <col min="4" max="4" width="20.125" customWidth="1"/>
     <col min="5" max="5" width="18.25" customWidth="1"/>
-    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="6" max="6" width="21.375" customWidth="1"/>
+    <col min="7" max="7" width="32.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" s="1" customFormat="1" spans="1:6">
@@ -1060,10 +1061,20 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2">
+        <v>100001</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2000</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2"/>

--- a/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -38,6 +38,9 @@
     <t>技能CD</t>
   </si>
   <si>
+    <t>buff执行栈</t>
+  </si>
+  <si>
     <t>#Note</t>
   </si>
   <si>
@@ -47,6 +50,9 @@
     <t>CD</t>
   </si>
   <si>
+    <t>BuffStacks</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
@@ -56,10 +62,16 @@
     <t>int</t>
   </si>
   <si>
+    <t>BuffStack[]</t>
+  </si>
+  <si>
     <t>普通攻击</t>
   </si>
   <si>
     <t>skill_1</t>
+  </si>
+  <si>
+    <t>[{"BuffId": 10000, "StartTime": 0}, {"BuffId": 20000, "StartTime": 100}]</t>
   </si>
 </sst>
 </file>
@@ -996,8 +1008,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A3:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="20.125" customWidth="1"/>
     <col min="5" max="5" width="18.25" customWidth="1"/>
@@ -1005,7 +1017,7 @@
     <col min="7" max="7" width="32.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" spans="1:7">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1015,68 +1027,83 @@
       <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
         <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2">
         <v>2000</v>
       </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>100001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2">
         <v>2000</v>
       </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1084,7 +1111,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="F9" s="2"/>
     </row>
   </sheetData>

--- a/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
@@ -27,15 +27,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>技能CD</t>
+  </si>
+  <si>
+    <t>是否技能动画</t>
+  </si>
+  <si>
+    <t>技能动画开始时间</t>
+  </si>
+  <si>
     <t>技能动画标签</t>
   </si>
   <si>
-    <t>技能CD</t>
+    <t>能否被打断</t>
+  </si>
+  <si>
+    <t>打断动画</t>
+  </si>
+  <si>
+    <t>Buff开始偏移释放时间</t>
   </si>
   <si>
     <t>buff执行栈</t>
@@ -44,10 +59,22 @@
     <t>#Note</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>IsSkillAnimation</t>
+  </si>
+  <si>
+    <t>SkillAnimationSTime</t>
+  </si>
+  <si>
     <t>SkillAniTag</t>
   </si>
   <si>
-    <t>CD</t>
+    <t>InterruptSkillAniTag</t>
+  </si>
+  <si>
+    <t>BuffOffSetSTime</t>
   </si>
   <si>
     <t>BuffStacks</t>
@@ -71,7 +98,7 @@
     <t>skill_1</t>
   </si>
   <si>
-    <t>[{"BuffId": 10000, "StartTime": 0}, {"BuffId": 20000, "StartTime": 100}]</t>
+    <t>[{"BuffId": 10000, "OffExecuteTime": 0}]</t>
   </si>
 </sst>
 </file>
@@ -1008,16 +1035,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A3:L9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="20.125" customWidth="1"/>
-    <col min="5" max="5" width="18.25" customWidth="1"/>
-    <col min="6" max="6" width="21.375" customWidth="1"/>
-    <col min="7" max="7" width="32.75" customWidth="1"/>
+    <col min="5" max="5" width="13.375" customWidth="1"/>
+    <col min="6" max="6" width="18.25" customWidth="1"/>
+    <col min="7" max="7" width="21.5" customWidth="1"/>
+    <col min="8" max="8" width="28.5" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="10" max="11" width="26" customWidth="1"/>
+    <col min="12" max="12" width="80.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" spans="1:12">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1030,89 +1061,172 @@
       <c r="G3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
+    <row r="4" s="1" customFormat="1" spans="1:12">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" spans="1:12">
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:12">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
         <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2000</v>
       </c>
       <c r="F6" s="2">
-        <v>2000</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:12">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>100001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2000</v>
       </c>
       <c r="F7" s="2">
-        <v>2000</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:12">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:7">
-      <c r="F9" s="2"/>
+    <row r="9" spans="1:12">
+      <c r="E9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17175"/>
   </bookViews>
   <sheets>
     <sheet name="SkillConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -98,7 +98,10 @@
     <t>skill_1</t>
   </si>
   <si>
-    <t>[{"BuffId": 10000, "OffExecuteTime": 0}]</t>
+    <t>[{"BuffId": 10000}, {"BuffId": 20001}]</t>
+  </si>
+  <si>
+    <t>[]</t>
   </si>
 </sst>
 </file>
@@ -1045,10 +1048,10 @@
     <col min="8" max="8" width="28.5" customWidth="1"/>
     <col min="9" max="9" width="13.5" customWidth="1"/>
     <col min="10" max="11" width="26" customWidth="1"/>
-    <col min="12" max="12" width="80.375" customWidth="1"/>
+    <col min="12" max="12" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="1:12">
+    <row r="3" s="1" customFormat="1" spans="3:12">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:12">
+    <row r="4" s="1" customFormat="1" spans="3:12">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1109,7 +1112,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
+    <row r="5" s="1" customFormat="1" spans="3:12">
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1169,7 +1172,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
@@ -1203,13 +1206,13 @@
         <v>22</v>
       </c>
       <c r="K7" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1222,7 +1225,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="5:11">
       <c r="E9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>

--- a/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -59,7 +59,7 @@
     <t>#Note</t>
   </si>
   <si>
-    <t>CD</t>
+    <t>CDTime</t>
   </si>
   <si>
     <t>IsSkillAnimation</t>
@@ -71,6 +71,9 @@
     <t>SkillAniTag</t>
   </si>
   <si>
+    <t>CanBeInterrupted</t>
+  </si>
+  <si>
     <t>InterruptSkillAniTag</t>
   </si>
   <si>
@@ -89,6 +92,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>BuffStack[]</t>
   </si>
   <si>
@@ -96,6 +102,9 @@
   </si>
   <si>
     <t>skill_1</t>
+  </si>
+  <si>
+    <t>skill_11</t>
   </si>
   <si>
     <t>[{"BuffId": 10000}, {"BuffId": 20001}]</t>
@@ -1046,7 +1055,7 @@
     <col min="6" max="6" width="18.25" customWidth="1"/>
     <col min="7" max="7" width="21.5" customWidth="1"/>
     <col min="8" max="8" width="28.5" customWidth="1"/>
-    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="18.25" customWidth="1"/>
     <col min="10" max="11" width="26" customWidth="1"/>
     <col min="12" max="12" width="51" customWidth="1"/>
   </cols>
@@ -1100,48 +1109,48 @@
         <v>13</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="3:12">
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1151,31 +1160,31 @@
         <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2">
-        <v>2000</v>
-      </c>
-      <c r="F6" s="2">
+        <v>750</v>
+      </c>
+      <c r="F6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="2">
+        <v>24</v>
+      </c>
+      <c r="I6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>22</v>
+      <c r="J6" t="s">
+        <v>25</v>
       </c>
       <c r="K6" s="2">
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1185,31 +1194,31 @@
         <v>100001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2">
-        <v>2000</v>
-      </c>
-      <c r="F7" s="2">
+        <v>750</v>
+      </c>
+      <c r="F7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="2">
+        <v>24</v>
+      </c>
+      <c r="I7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>22</v>
+      <c r="J7" t="s">
+        <v>25</v>
       </c>
       <c r="K7" s="2">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:11">

--- a/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/SkillConfig@玩家技能@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SkillConfig" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
     <t>打断动画</t>
   </si>
   <si>
-    <t>Buff开始偏移释放时间</t>
+    <t>buff栈开始偏移释放时间</t>
   </si>
   <si>
     <t>buff执行栈</t>
@@ -77,7 +77,7 @@
     <t>InterruptSkillAniTag</t>
   </si>
   <si>
-    <t>BuffOffSetSTime</t>
+    <t>BuffStackStartTime</t>
   </si>
   <si>
     <t>BuffStacks</t>
@@ -107,7 +107,7 @@
     <t>skill_11</t>
   </si>
   <si>
-    <t>[{"BuffId": 10000}, {"BuffId": 20001}]</t>
+    <t>[{"BuffId": 10000 , "StartTime": 0}, {"BuffId": 20001, "StartTime": 0}]</t>
   </si>
   <si>
     <t>[]</t>
@@ -1060,7 +1060,7 @@
     <col min="12" max="12" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="3:12">
+    <row r="3" s="1" customFormat="1" spans="1:12">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:12">
+    <row r="4" s="1" customFormat="1" spans="1:12">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:12">
+    <row r="5" s="1" customFormat="1" spans="1:12">
       <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1234,7 +1234,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="5:11">
+    <row r="9" spans="1:12">
       <c r="E9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
